--- a/output/Data and Chart Outputs/peru_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/peru_power_capacity.xlsx
@@ -364,6 +364,34 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E34948"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$I$2:$I$6</f>
+            </numRef>
+          </val>
+        </ser>
         <gapWidth val="30"/>
         <overlap val="100"/>
         <axId val="10"/>
@@ -452,7 +480,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -981,7 +1009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1015,17 +1043,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Bioenergy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Coal</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Oil</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bioenergy</t>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Nuclear &amp; other</t>
         </is>
       </c>
     </row>
@@ -1046,13 +1079,16 @@
         <v>0.28227</v>
       </c>
       <c r="F2" t="n">
+        <v>2.60348</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.06568</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.14071</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.60348</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.06568</v>
+      <c r="I2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1072,13 +1108,16 @@
         <v>0.28227</v>
       </c>
       <c r="F3" t="n">
+        <v>2.60108</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.06425</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.13977</v>
       </c>
-      <c r="G3" t="n">
-        <v>2.60108</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.06425</v>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1098,13 +1137,16 @@
         <v>0.28227</v>
       </c>
       <c r="F4" t="n">
+        <v>2.61954</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.06584999999999999</v>
+      </c>
+      <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.61954</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.06584999999999999</v>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1124,13 +1166,16 @@
         <v>0.47776</v>
       </c>
       <c r="F5" t="n">
+        <v>2.7236</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.06659999999999999</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.7236</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.06659999999999999</v>
+      <c r="I5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1150,13 +1195,16 @@
         <v>0.9346599999999999</v>
       </c>
       <c r="F6" t="n">
+        <v>2.7094</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.10701</v>
+      </c>
+      <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.7094</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.10701</v>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/peru_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/peru_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -826,7 +827,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -841,7 +841,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -870,7 +869,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -934,7 +932,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
@@ -1063,7 +1060,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1092,7 +1089,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -1121,7 +1118,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1150,7 +1147,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1179,7 +1176,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">

--- a/output/Data and Chart Outputs/peru_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/peru_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -158,6 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Peru installed generation capacity (COES) (to 2025)</a:t>
             </a:r>
           </a:p>
@@ -291,7 +291,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -319,7 +319,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -347,7 +347,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -375,7 +375,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -827,6 +827,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -841,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -869,6 +871,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -932,6 +935,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
@@ -1060,7 +1064,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1089,7 +1093,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -1118,7 +1122,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1147,7 +1151,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1176,7 +1180,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">

--- a/output/Data and Chart Outputs/peru_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/peru_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -827,7 +828,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -842,7 +842,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -871,7 +870,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -935,7 +933,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
@@ -1064,7 +1061,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1093,7 +1090,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -1122,7 +1119,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1151,7 +1148,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1180,7 +1177,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">

--- a/output/Data and Chart Outputs/peru_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/peru_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -828,6 +827,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -842,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -870,6 +871,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -933,6 +935,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
@@ -1061,7 +1064,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1090,7 +1093,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -1119,7 +1122,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1148,7 +1151,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1177,7 +1180,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">
